--- a/rules/CORE-002000/negative/01/data/CORE-002000-negative-01.xlsx
+++ b/rules/CORE-002000/negative/01/data/CORE-002000-negative-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/negative/01/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/CORE-002000/negative/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEA5BF1-BB9C-0048-959C-62D404ABEEF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349B50D4-1F38-7B49-ADF5-3DC145BA7DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>Product</t>
   </si>
@@ -110,6 +110,18 @@
   </si>
   <si>
     <t>[ABSENT]</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>define_dataset_class</t>
+  </si>
+  <si>
+    <t>EVENTS</t>
+  </si>
+  <si>
+    <t>domain</t>
   </si>
 </sst>
 </file>
@@ -538,7 +550,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -571,8 +583,8 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2">
-        <v>1</v>
+      <c r="D2" t="s">
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
@@ -581,8 +593,49 @@
         <v>28</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
